--- a/LISTAS/mi/CINTA EMBALAR.xlsx
+++ b/LISTAS/mi/CINTA EMBALAR.xlsx
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="15.140625" customWidth="1" style="8" min="1" max="1"/>
@@ -819,14 +819,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="n">
-        <v>45177.60123984873</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="8">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,8 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="8">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -888,7 +882,6 @@
       <c r="D14" s="21" t="n"/>
     </row>
     <row r="15" ht="290.25" customHeight="1" s="8"/>
-    <row r="16"/>
     <row r="17" ht="18" customHeight="1" s="8">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -936,20 +929,19 @@
       </c>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="18" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="20"/>
+        <v>440</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CINTA EMBALAR.xlsx
+++ b/LISTAS/mi/CINTA EMBALAR.xlsx
@@ -819,7 +819,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/mi/CINTA EMBALAR.xlsx
+++ b/LISTAS/mi/CINTA EMBALAR.xlsx
@@ -819,7 +819,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/mi/CINTA EMBALAR.xlsx
+++ b/LISTAS/mi/CINTA EMBALAR.xlsx
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="15.140625" customWidth="1" style="8" min="1" max="1"/>
@@ -819,10 +819,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="n">
-        <v>45266</v>
+        <v>45226.65150480779</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="8">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -844,6 +848,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="8">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -882,6 +888,7 @@
       <c r="D14" s="21" t="n"/>
     </row>
     <row r="15" ht="290.25" customHeight="1" s="8"/>
+    <row r="16"/>
     <row r="17" ht="18" customHeight="1" s="8">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -913,7 +920,7 @@
       </c>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="18" t="n">
-        <v>404</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="8">
@@ -929,19 +936,20 @@
       </c>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="18" t="n">
-        <v>440</v>
-      </c>
-    </row>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="20"/>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CINTA EMBALAR.xlsx
+++ b/LISTAS/mi/CINTA EMBALAR.xlsx
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="15.140625" customWidth="1" style="8" min="1" max="1"/>
@@ -819,14 +819,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="n">
-        <v>45226.65150480779</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="8">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,8 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="8">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -888,7 +882,6 @@
       <c r="D14" s="21" t="n"/>
     </row>
     <row r="15" ht="290.25" customHeight="1" s="8"/>
-    <row r="16"/>
     <row r="17" ht="18" customHeight="1" s="8">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -936,20 +929,19 @@
       </c>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="18" t="n">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="20"/>
+        <v>440</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
